--- a/AR/AR invoice Template .xlsx
+++ b/AR/AR invoice Template .xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\MSIGSX\AR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{756CF398-DCA6-4D49-A754-1ECB7B1B8C14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E788C4BB-E8DB-4BDE-84F0-3B171C300BBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="48" windowWidth="30936" windowHeight="16776" xr2:uid="{D3F70513-4056-4EC3-ADC2-9276ACB3237B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D3F70513-4056-4EC3-ADC2-9276ACB3237B}"/>
   </bookViews>
   <sheets>
     <sheet name="AR_Head" sheetId="2" r:id="rId1"/>
@@ -633,7 +633,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2321" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2321" uniqueCount="267">
   <si>
     <t>ParentKey</t>
   </si>
@@ -1404,6 +1404,36 @@
   </si>
   <si>
     <t>(ຈຳເປັນຕ້ອງໃສ່ຕະຫລອດບໍ່ມີປ່ຽນ)</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>10</t>
   </si>
 </sst>
 </file>
@@ -1535,7 +1565,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1584,6 +1614,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -1629,7 +1665,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1780,6 +1816,22 @@
     <xf numFmtId="0" fontId="17" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="8" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2153,13 +2205,13 @@
   <cols>
     <col min="1" max="1" width="12.59765625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="37.69921875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.3984375" style="64" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.3984375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.3984375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.796875" customWidth="1"/>
     <col min="8" max="8" width="19" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.09765625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.09765625" style="67" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.8984375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="20.5" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="34.09765625" bestFit="1" customWidth="1"/>
@@ -2172,7 +2224,7 @@
       <c r="B1" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="C1" s="36" t="s">
+      <c r="C1" s="62" t="s">
         <v>21</v>
       </c>
       <c r="D1" s="37" t="s">
@@ -2190,7 +2242,7 @@
       <c r="H1" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="I1" s="36" t="s">
+      <c r="I1" s="65" t="s">
         <v>27</v>
       </c>
       <c r="J1" s="36" t="s">
@@ -2200,7 +2252,7 @@
         <v>33</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>237</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -2210,7 +2262,7 @@
       <c r="B2" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="38" t="s">
+      <c r="C2" s="63" t="s">
         <v>21</v>
       </c>
       <c r="D2" s="39" t="s">
@@ -2228,7 +2280,7 @@
       <c r="H2" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="I2" s="38" t="s">
+      <c r="I2" s="66" t="s">
         <v>29</v>
       </c>
       <c r="J2" s="38" t="s">
@@ -2238,17 +2290,17 @@
         <v>33</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>237</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="59" t="s">
-        <v>203</v>
+        <v>257</v>
       </c>
       <c r="B3">
         <v>99</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="64" t="s">
         <v>30</v>
       </c>
       <c r="D3" s="5">
@@ -2264,7 +2316,7 @@
         <v>206</v>
       </c>
       <c r="H3" s="5"/>
-      <c r="I3" t="s">
+      <c r="I3" s="67" t="s">
         <v>16</v>
       </c>
       <c r="K3" s="7" t="s">
@@ -2276,12 +2328,12 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="59" t="s">
-        <v>204</v>
+        <v>258</v>
       </c>
       <c r="B4">
         <v>99</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="64" t="s">
         <v>30</v>
       </c>
       <c r="D4" s="5">
@@ -2297,7 +2349,7 @@
         <v>207</v>
       </c>
       <c r="H4" s="5"/>
-      <c r="I4" t="s">
+      <c r="I4" s="67" t="s">
         <v>16</v>
       </c>
       <c r="K4" s="7" t="s">
@@ -2309,12 +2361,12 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="59" t="s">
-        <v>205</v>
+        <v>259</v>
       </c>
       <c r="B5">
         <v>99</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="64" t="s">
         <v>30</v>
       </c>
       <c r="D5" s="5">
@@ -2330,7 +2382,7 @@
         <v>208</v>
       </c>
       <c r="H5" s="5"/>
-      <c r="I5" t="s">
+      <c r="I5" s="67" t="s">
         <v>16</v>
       </c>
       <c r="K5" s="7" t="s">
@@ -2340,14 +2392,14 @@
         <v>202</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="60" t="s">
-        <v>221</v>
+    <row r="6" spans="1:12" ht="15" x14ac:dyDescent="0.25">
+      <c r="A6" s="59" t="s">
+        <v>260</v>
       </c>
       <c r="B6">
         <v>99</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="64" t="s">
         <v>30</v>
       </c>
       <c r="D6" s="5">
@@ -2362,7 +2414,7 @@
       <c r="G6" t="s">
         <v>230</v>
       </c>
-      <c r="I6" t="s">
+      <c r="I6" s="67" t="s">
         <v>16</v>
       </c>
       <c r="K6" t="s">
@@ -2372,14 +2424,14 @@
         <v>202</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="60" t="s">
-        <v>222</v>
+    <row r="7" spans="1:12" ht="15" x14ac:dyDescent="0.25">
+      <c r="A7" s="59" t="s">
+        <v>261</v>
       </c>
       <c r="B7">
         <v>99</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="64" t="s">
         <v>30</v>
       </c>
       <c r="D7" s="5">
@@ -2394,7 +2446,7 @@
       <c r="G7" t="s">
         <v>231</v>
       </c>
-      <c r="I7" t="s">
+      <c r="I7" s="67" t="s">
         <v>16</v>
       </c>
       <c r="K7" t="s">
@@ -2404,14 +2456,14 @@
         <v>165</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="60" t="s">
-        <v>223</v>
+    <row r="8" spans="1:12" ht="15" x14ac:dyDescent="0.25">
+      <c r="A8" s="59" t="s">
+        <v>262</v>
       </c>
       <c r="B8">
         <v>99</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="64" t="s">
         <v>30</v>
       </c>
       <c r="D8" s="5">
@@ -2426,7 +2478,7 @@
       <c r="G8" t="s">
         <v>232</v>
       </c>
-      <c r="I8" t="s">
+      <c r="I8" s="67" t="s">
         <v>16</v>
       </c>
       <c r="K8" t="s">
@@ -2436,14 +2488,14 @@
         <v>193</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="60" t="s">
-        <v>224</v>
+    <row r="9" spans="1:12" ht="15" x14ac:dyDescent="0.25">
+      <c r="A9" s="59" t="s">
+        <v>263</v>
       </c>
       <c r="B9">
         <v>99</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="64" t="s">
         <v>30</v>
       </c>
       <c r="D9" s="5">
@@ -2458,7 +2510,7 @@
       <c r="G9" t="s">
         <v>233</v>
       </c>
-      <c r="I9" t="s">
+      <c r="I9" s="67" t="s">
         <v>16</v>
       </c>
       <c r="K9" t="s">
@@ -2468,14 +2520,14 @@
         <v>202</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="60" t="s">
-        <v>225</v>
+    <row r="10" spans="1:12" ht="15" x14ac:dyDescent="0.25">
+      <c r="A10" s="59" t="s">
+        <v>264</v>
       </c>
       <c r="B10">
         <v>99</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="64" t="s">
         <v>30</v>
       </c>
       <c r="D10" s="5">
@@ -2490,7 +2542,7 @@
       <c r="G10" t="s">
         <v>234</v>
       </c>
-      <c r="I10" t="s">
+      <c r="I10" s="67" t="s">
         <v>16</v>
       </c>
       <c r="K10" t="s">
@@ -2500,14 +2552,14 @@
         <v>165</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="60" t="s">
-        <v>226</v>
+    <row r="11" spans="1:12" ht="15" x14ac:dyDescent="0.25">
+      <c r="A11" s="59" t="s">
+        <v>265</v>
       </c>
       <c r="B11">
         <v>99</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="64" t="s">
         <v>30</v>
       </c>
       <c r="D11" s="5">
@@ -2522,7 +2574,7 @@
       <c r="G11" t="s">
         <v>235</v>
       </c>
-      <c r="I11" t="s">
+      <c r="I11" s="67" t="s">
         <v>16</v>
       </c>
       <c r="K11" t="s">
@@ -2532,14 +2584,14 @@
         <v>193</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="60" t="s">
-        <v>227</v>
+    <row r="12" spans="1:12" ht="15" x14ac:dyDescent="0.25">
+      <c r="A12" s="59" t="s">
+        <v>266</v>
       </c>
       <c r="B12">
         <v>99</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="64" t="s">
         <v>30</v>
       </c>
       <c r="D12" s="5">
@@ -2554,7 +2606,7 @@
       <c r="G12" t="s">
         <v>236</v>
       </c>
-      <c r="I12" t="s">
+      <c r="I12" s="67" t="s">
         <v>16</v>
       </c>
       <c r="K12" t="s">
@@ -3424,7 +3476,7 @@
     </row>
     <row r="3" spans="1:139" s="57" customFormat="1" ht="15.6" x14ac:dyDescent="0.4">
       <c r="A3" s="40" t="s">
-        <v>203</v>
+        <v>257</v>
       </c>
       <c r="B3" s="40">
         <v>0</v>
@@ -3842,8 +3894,8 @@
       </c>
     </row>
     <row r="4" spans="1:139" ht="15.6" x14ac:dyDescent="0.4">
-      <c r="A4" s="1" t="s">
-        <v>203</v>
+      <c r="A4" s="40" t="s">
+        <v>257</v>
       </c>
       <c r="B4" s="1">
         <v>1</v>
@@ -4261,8 +4313,8 @@
       </c>
     </row>
     <row r="5" spans="1:139" ht="15.6" x14ac:dyDescent="0.4">
-      <c r="A5" s="1" t="s">
-        <v>203</v>
+      <c r="A5" s="40" t="s">
+        <v>257</v>
       </c>
       <c r="B5" s="1">
         <v>2</v>
@@ -4681,7 +4733,7 @@
     </row>
     <row r="6" spans="1:139" s="57" customFormat="1" ht="16.8" x14ac:dyDescent="0.5">
       <c r="A6" s="40" t="s">
-        <v>204</v>
+        <v>258</v>
       </c>
       <c r="B6" s="40">
         <v>0</v>
@@ -5099,8 +5151,8 @@
       </c>
     </row>
     <row r="7" spans="1:139" ht="16.8" x14ac:dyDescent="0.5">
-      <c r="A7" s="1" t="s">
-        <v>204</v>
+      <c r="A7" s="40" t="s">
+        <v>258</v>
       </c>
       <c r="B7" s="1">
         <v>1</v>
@@ -5518,8 +5570,8 @@
       </c>
     </row>
     <row r="8" spans="1:139" ht="16.8" x14ac:dyDescent="0.5">
-      <c r="A8" s="1" t="s">
-        <v>204</v>
+      <c r="A8" s="40" t="s">
+        <v>258</v>
       </c>
       <c r="B8" s="1">
         <v>2</v>
@@ -5938,7 +5990,7 @@
     </row>
     <row r="9" spans="1:139" s="57" customFormat="1" ht="15.6" x14ac:dyDescent="0.4">
       <c r="A9" s="40" t="s">
-        <v>205</v>
+        <v>259</v>
       </c>
       <c r="B9" s="40">
         <v>0</v>
@@ -6356,8 +6408,8 @@
       </c>
     </row>
     <row r="10" spans="1:139" ht="15.6" x14ac:dyDescent="0.4">
-      <c r="A10" s="1" t="s">
-        <v>205</v>
+      <c r="A10" s="40" t="s">
+        <v>259</v>
       </c>
       <c r="B10" s="1">
         <v>1</v>
@@ -6775,8 +6827,8 @@
       </c>
     </row>
     <row r="11" spans="1:139" ht="15.6" x14ac:dyDescent="0.4">
-      <c r="A11" s="1" t="s">
-        <v>205</v>
+      <c r="A11" s="40" t="s">
+        <v>259</v>
       </c>
       <c r="B11" s="1">
         <v>2</v>
@@ -14735,7 +14787,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="30" spans="1:139" s="57" customFormat="1" ht="15.6" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:139" s="57" customFormat="1" ht="16.8" x14ac:dyDescent="0.5">
       <c r="A30" s="40" t="s">
         <v>227</v>
       </c>
